--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,459 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128913459</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hästbergs klack Granticka, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>503561</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6688337</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128913280</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80225</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hästbergs klack, Lunglav 1 Rönn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>503628</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6688322</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket fin växtplats med ett stort antal små lober under de två stora.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128913698</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56898</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hästbergs klack Järpe, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>503613</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6688351</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sisande järptupp</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128913382</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80225</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hästbergs klack Lunglav 2 Sälg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>503594</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6688339</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Frisk och fin, ymnig med många små lober.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128913280</v>
       </c>
       <c r="B4" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>128913698</v>
       </c>
       <c r="B5" t="n">
-        <v>56898</v>
+        <v>56901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128913382</v>
       </c>
       <c r="B6" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128913280</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>128913698</v>
       </c>
       <c r="B5" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128913382</v>
       </c>
       <c r="B6" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128913280</v>
       </c>
       <c r="B4" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128913382</v>
       </c>
       <c r="B6" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128913280</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>128913698</v>
       </c>
       <c r="B5" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128913382</v>
       </c>
       <c r="B6" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>128913280</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>128913698</v>
       </c>
       <c r="B5" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>128913382</v>
       </c>
       <c r="B6" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,14 +817,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128913280</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>128913382</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>128913280</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>128913382</v>
       </c>
       <c r="B6" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>128913459</v>
       </c>
       <c r="B3" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41456-2025 artfynd.xlsx
+++ b/artfynd/A 41456-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>126838</v>
       </c>
       <c r="B2" t="n">
-        <v>78479</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>503568.812065361</v>
+        <v>503569</v>
       </c>
       <c r="R2" t="n">
-        <v>6688335.033783657</v>
+        <v>6688335</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2002-05-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-05-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128913459</v>
+        <v>128913280</v>
       </c>
       <c r="B3" t="n">
-        <v>91569</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,30 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hästbergs klack Granticka, Dlr</t>
+          <t>Hästbergs klack, Lunglav 1 Rönn, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503561</v>
+        <v>503628</v>
       </c>
       <c r="R3" t="n">
-        <v>6688337</v>
+        <v>6688322</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +855,11 @@
           <t>2025-10-02</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mycket fin växtplats med ett stort antal små lober under de två stora.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -877,17 +871,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -905,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128913280</v>
+        <v>128913382</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,14 +930,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästbergs klack, Lunglav 1 Rönn, Dlr</t>
+          <t>Hästbergs klack Lunglav 2 Sälg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>503628</v>
+        <v>503594</v>
       </c>
       <c r="R4" t="n">
-        <v>6688322</v>
+        <v>6688339</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +974,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mycket fin växtplats med ett stort antal små lober under de två stora.</t>
+          <t>Frisk och fin, ymnig med många små lober.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,17 +988,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1025,11 +1019,11 @@
         <v>128913698</v>
       </c>
       <c r="B5" t="n">
-        <v>56908</v>
+        <v>57132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1126,123 +1120,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>128913382</v>
-      </c>
-      <c r="B6" t="n">
-        <v>80149</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Hästbergs klack Lunglav 2 Sälg, Dlr</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>503594</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6688339</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Grangärde</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-10-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Frisk och fin, ymnig med många små lober.</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Tobias Hellberg</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
